--- a/nebius/docs/reports/20261008_nebius_v0.3_收入錨定.xlsx
+++ b/nebius/docs/reports/20261008_nebius_v0.3_收入錨定.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="敏感度" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目標價變動拆解" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本端評估" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司實況驗證" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +519,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.15913942625215</v>
+        <v>8.825199907724254</v>
       </c>
       <c r="C4" t="n">
-        <v>15.04667220393632</v>
+        <v>9.21179827155456</v>
       </c>
       <c r="D4" t="n">
-        <v>17.970334094296</v>
+        <v>9.406764831885297</v>
       </c>
       <c r="E4" t="n">
-        <v>19.20577108987948</v>
+        <v>9.488753147301413</v>
       </c>
       <c r="F4" t="n">
-        <v>19.80275104443119</v>
+        <v>9.527934115409884</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +541,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.539139426252147</v>
+        <v>-2.794800092275747</v>
       </c>
       <c r="C5" t="n">
-        <v>3.42667220393632</v>
+        <v>-2.408201728445441</v>
       </c>
       <c r="D5" t="n">
-        <v>6.350334094295999</v>
+        <v>-2.213235168114704</v>
       </c>
       <c r="E5" t="n">
-        <v>7.585771089879479</v>
+        <v>-2.131246852698588</v>
       </c>
       <c r="F5" t="n">
-        <v>8.182751044431189</v>
+        <v>-2.092065884590117</v>
       </c>
     </row>
     <row r="6">
@@ -584,19 +585,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.15913942625215</v>
+        <v>8.825199907724254</v>
       </c>
       <c r="C7" t="n">
-        <v>15.04667220393632</v>
+        <v>9.21179827155456</v>
       </c>
       <c r="D7" t="n">
-        <v>17.970334094296</v>
+        <v>9.406764831885297</v>
       </c>
       <c r="E7" t="n">
-        <v>19.20577108987948</v>
+        <v>9.488753147301413</v>
       </c>
       <c r="F7" t="n">
-        <v>19.87481714355207</v>
+        <v>9.532645136058623</v>
       </c>
     </row>
     <row r="8">
@@ -606,19 +607,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.240860573747851</v>
+        <v>-8.574800092275744</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.353327796063677</v>
+        <v>-8.188201728445438</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5703340942960011</v>
+        <v>-7.993235168114701</v>
       </c>
       <c r="E8" t="n">
-        <v>1.805771089879482</v>
+        <v>-7.911246852698586</v>
       </c>
       <c r="F8" t="n">
-        <v>2.47481714355207</v>
+        <v>-7.867354863941376</v>
       </c>
     </row>
     <row r="9">
@@ -650,19 +651,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.15913942625215</v>
+        <v>8.825199907724254</v>
       </c>
       <c r="C10" t="n">
-        <v>15.84634740206162</v>
+        <v>9.265127846977622</v>
       </c>
       <c r="D10" t="n">
-        <v>18.80398949827732</v>
+        <v>9.460721939690298</v>
       </c>
       <c r="E10" t="n">
-        <v>19.91955922426279</v>
+        <v>9.53453623504414</v>
       </c>
       <c r="F10" t="n">
-        <v>20.49059624618219</v>
+        <v>9.571941299523559</v>
       </c>
     </row>
     <row r="11">
@@ -672,19 +673,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-10.04086057374785</v>
+        <v>-15.37480009227574</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.353652597938378</v>
+        <v>-14.93487215302238</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.396010501722674</v>
+        <v>-14.7392780603097</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.280440775737205</v>
+        <v>-14.66546376495586</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.709403753817814</v>
+        <v>-14.62805870047644</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +717,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tokenomics v5.27（20261008_Tokenomics_v5.27.xlsx，合併 19d667f）；k_長約 0.76、k_現貨 1.76</t>
+          <t>Tokenomics v5.27（20261008_Tokenomics_v5.27.xlsx，合併 19d667f）；第 2 輪 k＝隨需占比 0% × k_現貨 1.76＋其餘 × k_長約 0.76</t>
         </is>
       </c>
     </row>
@@ -777,7 +778,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>保守 已簽約 3.5 GW｜長約占比</t>
+          <t>保守 已簽約 3.5 GW｜長約占比（對照，不驅動）</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -799,23 +800,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>保守 已簽約 3.5 GW｜定價倍數 k</t>
+          <t>保守 已簽約 3.5 GW｜定價倍數 k（隨需 0%＝k_長約）</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.219343026386645</v>
+        <v>0.76</v>
       </c>
       <c r="C5" t="n">
-        <v>1.241393975191967</v>
+        <v>0.76</v>
       </c>
       <c r="D5" t="n">
-        <v>1.45187576767854</v>
+        <v>0.76</v>
       </c>
       <c r="E5" t="n">
-        <v>1.538282828282828</v>
+        <v>0.76</v>
       </c>
       <c r="F5" t="n">
-        <v>1.57957544746522</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="6">
@@ -825,19 +826,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.15913942625215</v>
+        <v>8.825199907724254</v>
       </c>
       <c r="C6" t="n">
-        <v>15.04667220393632</v>
+        <v>9.21179827155456</v>
       </c>
       <c r="D6" t="n">
-        <v>17.970334094296</v>
+        <v>9.406764831885297</v>
       </c>
       <c r="E6" t="n">
-        <v>19.20577108987948</v>
+        <v>9.488753147301413</v>
       </c>
       <c r="F6" t="n">
-        <v>19.80275104443119</v>
+        <v>9.527934115409884</v>
       </c>
     </row>
     <row r="7">
@@ -847,19 +848,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.692747598037188</v>
+        <v>0.4317801989391271</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5606609986369803</v>
+        <v>0.343245067625057</v>
       </c>
       <c r="D7" t="n">
-        <v>0.536719182107594</v>
+        <v>0.2809514336436573</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5086801002492045</v>
+        <v>0.2513171629309223</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4975728386476649</v>
+        <v>0.2394031623997826</v>
       </c>
     </row>
     <row r="8">
@@ -975,7 +976,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>基準 合約 5 GW｜長約占比</t>
+          <t>基準 合約 5 GW｜長約占比（對照，不驅動）</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -997,23 +998,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>基準 合約 5 GW｜定價倍數 k</t>
+          <t>基準 合約 5 GW｜定價倍數 k（隨需 0%＝k_長約）</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.219343026386645</v>
+        <v>0.76</v>
       </c>
       <c r="C14" t="n">
-        <v>1.241393975191967</v>
+        <v>0.76</v>
       </c>
       <c r="D14" t="n">
-        <v>1.45187576767854</v>
+        <v>0.76</v>
       </c>
       <c r="E14" t="n">
-        <v>1.538282828282828</v>
+        <v>0.76</v>
       </c>
       <c r="F14" t="n">
-        <v>1.584540367705835</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="15">
@@ -1023,19 +1024,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.15913942625215</v>
+        <v>8.825199907724254</v>
       </c>
       <c r="C15" t="n">
-        <v>15.04667220393632</v>
+        <v>9.21179827155456</v>
       </c>
       <c r="D15" t="n">
-        <v>17.970334094296</v>
+        <v>9.406764831885297</v>
       </c>
       <c r="E15" t="n">
-        <v>19.20577108987948</v>
+        <v>9.488753147301413</v>
       </c>
       <c r="F15" t="n">
-        <v>19.87481714355207</v>
+        <v>9.532645136058623</v>
       </c>
     </row>
     <row r="16">
@@ -1045,19 +1046,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.692747598037188</v>
+        <v>0.4317801989391271</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5606609986369803</v>
+        <v>0.343245067625057</v>
       </c>
       <c r="D16" t="n">
-        <v>0.536719182107594</v>
+        <v>0.2809514336436573</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5086801002492045</v>
+        <v>0.2513171629309223</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4963208035870282</v>
+        <v>0.2380525093672893</v>
       </c>
     </row>
     <row r="17">
@@ -1173,7 +1174,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>積極 每年 &gt;1 GW｜長約占比</t>
+          <t>積極 每年 &gt;1 GW｜長約占比（對照，不驅動）</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1195,23 +1196,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>積極 每年 &gt;1 GW｜定價倍數 k</t>
+          <t>積極 每年 &gt;1 GW｜定價倍數 k（隨需 0%＝k_長約）</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.219343026386645</v>
+        <v>0.76</v>
       </c>
       <c r="C23" t="n">
-        <v>1.299844343701685</v>
+        <v>0.76</v>
       </c>
       <c r="D23" t="n">
-        <v>1.510564638702254</v>
+        <v>0.76</v>
       </c>
       <c r="E23" t="n">
-        <v>1.587792487986663</v>
+        <v>0.76</v>
       </c>
       <c r="F23" t="n">
-        <v>1.626927355673775</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="24">
@@ -1221,19 +1222,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14.15913942625215</v>
+        <v>8.825199907724254</v>
       </c>
       <c r="C24" t="n">
-        <v>15.84634740206162</v>
+        <v>9.265127846977622</v>
       </c>
       <c r="D24" t="n">
-        <v>18.80398949827732</v>
+        <v>9.460721939690298</v>
       </c>
       <c r="E24" t="n">
-        <v>19.91955922426279</v>
+        <v>9.53453623504414</v>
       </c>
       <c r="F24" t="n">
-        <v>20.49059624618219</v>
+        <v>9.571941299523559</v>
       </c>
     </row>
     <row r="25">
@@ -1243,19 +1244,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.692747598037188</v>
+        <v>0.4317801989391271</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5651637754930037</v>
+        <v>0.3304430037765037</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5370593492884876</v>
+        <v>0.2702069775775438</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5074026923749386</v>
+        <v>0.2428692975452549</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4948339468655886</v>
+        <v>0.2311558646465197</v>
       </c>
     </row>
     <row r="26">
@@ -2742,7 +2743,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>165</v>
+        <v>264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2782,7 +2783,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14.1163636363636</v>
+        <v>8.822727272727271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2837,7 +2838,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.24775334314822</v>
+        <v>0.77984583946764</v>
       </c>
     </row>
     <row r="11">
@@ -2852,7 +2853,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14.1591394262521</v>
+        <v>8.825199907724249</v>
       </c>
     </row>
     <row r="12">
@@ -2882,7 +2883,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.21934302638665</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="14">
@@ -2897,7 +2898,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.79520500002264</v>
+        <v>2.46126548149474</v>
       </c>
     </row>
     <row r="15">
@@ -2912,7 +2913,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.22490341319264</v>
+        <v>0.386752175093198</v>
       </c>
     </row>
     <row r="16">
@@ -2927,7 +2928,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.75242921013413</v>
+        <v>2.45879284649777</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2947,7 +2948,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.32141798267503</v>
+        <v>-0.224524412723474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2967,7 +2968,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.364193772563541</v>
+        <v>0.226997047720453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3023,7 +3024,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>類型：觀點／已知限制。差距幾乎全部來自 (i) 爬坡分母——6/30 在役約 366 MW（內插）中只有約 165 MW 依 Q2 營收計費（Microsoft 全部 tranche 於第二季下半季才交付、其他新容量第二季下半季上線），模型把差距歸為爬坡而非低價；Q2 隱含 k（÷ 在役）約 0.56 只列不用。季末在役 MW 公司未揭露（資料缺口），Q3 揭露後重估。</t>
+          <t>類型：觀點／已知限制。差距幾乎全部來自 (i) 爬坡分母——6/30 在役約 366 MW（內插）中只有約 264 MW 依 Q2 營收計費（Microsoft 全部 tranche 於第二季下半季才交付、其他新容量第二季下半季上線），模型把差距歸為爬坡而非低價；Q2 隱含 k（÷ 在役）約 0.56 只列不用。季末在役 MW 公司未揭露（資料缺口），Q3 揭露後重估。</t>
         </is>
       </c>
     </row>
@@ -3119,31 +3120,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.334594</v>
+        <v>18.867705</v>
       </c>
       <c r="C3" t="n">
-        <v>81.753432</v>
+        <v>23.498253</v>
       </c>
       <c r="D3" t="n">
-        <v>176.902878</v>
+        <v>39.19802</v>
       </c>
       <c r="E3" t="n">
-        <v>41.345162</v>
+        <v>61.488452</v>
       </c>
       <c r="F3" t="n">
-        <v>30.984731</v>
+        <v>61.238371</v>
       </c>
       <c r="G3" t="n">
-        <v>8.604194</v>
+        <v>55.795512</v>
       </c>
       <c r="H3" t="n">
-        <v>53.001381</v>
+        <v>75.45209</v>
       </c>
       <c r="I3" t="n">
-        <v>45.12156</v>
+        <v>73.186127</v>
       </c>
       <c r="J3" t="n">
-        <v>27.637011</v>
+        <v>64.120262</v>
       </c>
     </row>
     <row r="4">
@@ -3153,31 +3154,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55.274618</v>
+        <v>13.45964</v>
       </c>
       <c r="C4" t="n">
-        <v>72.53416799999999</v>
+        <v>17.248317</v>
       </c>
       <c r="D4" t="n">
-        <v>161.690131</v>
+        <v>32.911313</v>
       </c>
       <c r="E4" t="n">
-        <v>38.085995</v>
+        <v>54.607902</v>
       </c>
       <c r="F4" t="n">
-        <v>28.529909</v>
+        <v>53.190374</v>
       </c>
       <c r="G4" t="n">
-        <v>7.372383</v>
+        <v>46.891325</v>
       </c>
       <c r="H4" t="n">
-        <v>63.739285</v>
+        <v>86.515804</v>
       </c>
       <c r="I4" t="n">
-        <v>55.753491</v>
+        <v>84.22532</v>
       </c>
       <c r="J4" t="n">
-        <v>38.048679</v>
+        <v>75.06137099999999</v>
       </c>
     </row>
     <row r="5">
@@ -3187,31 +3188,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.83580499999999</v>
+        <v>6.06379</v>
       </c>
       <c r="C5" t="n">
-        <v>87.815451</v>
+        <v>12.150587</v>
       </c>
       <c r="D5" t="n">
-        <v>202.85043</v>
+        <v>33.375786</v>
       </c>
       <c r="E5" t="n">
-        <v>46.754049</v>
+        <v>61.727885</v>
       </c>
       <c r="F5" t="n">
-        <v>33.553838</v>
+        <v>61.727885</v>
       </c>
       <c r="G5" t="n">
-        <v>6.412298</v>
+        <v>57.191432</v>
       </c>
       <c r="H5" t="n">
-        <v>91.09259900000001</v>
+        <v>122.285168</v>
       </c>
       <c r="I5" t="n">
-        <v>80.367125</v>
+        <v>119.359016</v>
       </c>
       <c r="J5" t="n">
-        <v>56.963622</v>
+        <v>107.652395</v>
       </c>
     </row>
   </sheetData>
@@ -3225,7 +3226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3299,31 +3300,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.753432</v>
+        <v>23.498253</v>
       </c>
       <c r="C2" t="n">
-        <v>72.53416799999999</v>
+        <v>17.248317</v>
       </c>
       <c r="D2" t="n">
-        <v>87.815451</v>
+        <v>12.150587</v>
       </c>
       <c r="E2" t="n">
-        <v>30.984731</v>
+        <v>61.238371</v>
       </c>
       <c r="F2" t="n">
-        <v>28.529909</v>
+        <v>53.190374</v>
       </c>
       <c r="G2" t="n">
-        <v>33.553838</v>
+        <v>61.727885</v>
       </c>
       <c r="H2" t="n">
-        <v>45.12156</v>
+        <v>73.186127</v>
       </c>
       <c r="I2" t="n">
-        <v>55.753491</v>
+        <v>84.22532</v>
       </c>
       <c r="J2" t="n">
-        <v>80.367125</v>
+        <v>119.359016</v>
       </c>
     </row>
     <row r="3">
@@ -3333,337 +3334,405 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.609359</v>
+        <v>18.867705</v>
       </c>
       <c r="C3" t="n">
-        <v>71.283734</v>
+        <v>13.45964</v>
       </c>
       <c r="D3" t="n">
-        <v>86.54955699999999</v>
+        <v>6.06379</v>
       </c>
       <c r="E3" t="n">
-        <v>31.595233</v>
+        <v>61.488452</v>
       </c>
       <c r="F3" t="n">
-        <v>29.246024</v>
+        <v>54.607902</v>
       </c>
       <c r="G3" t="n">
-        <v>34.274787</v>
+        <v>61.727885</v>
       </c>
       <c r="H3" t="n">
-        <v>45.704941</v>
+        <v>75.45209</v>
       </c>
       <c r="I3" t="n">
-        <v>56.336957</v>
+        <v>86.515804</v>
       </c>
       <c r="J3" t="n">
-        <v>80.955055</v>
+        <v>122.285168</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>k_長約 1.00</t>
+          <t>k_長約 0.89（三筆長約中位數）</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90.55625999999999</v>
+        <v>32.79984</v>
       </c>
       <c r="C4" t="n">
-        <v>77.69544999999999</v>
+        <v>25.796265</v>
       </c>
       <c r="D4" t="n">
-        <v>93.030208</v>
+        <v>24.2727</v>
       </c>
       <c r="E4" t="n">
-        <v>28.546584</v>
+        <v>59.560273</v>
       </c>
       <c r="F4" t="n">
-        <v>25.66931</v>
+        <v>50.118806</v>
       </c>
       <c r="G4" t="n">
-        <v>30.673903</v>
+        <v>60.332628</v>
       </c>
       <c r="H4" t="n">
-        <v>42.791771</v>
+        <v>68.276292</v>
       </c>
       <c r="I4" t="n">
-        <v>53.423361</v>
+        <v>79.262356</v>
       </c>
       <c r="J4" t="n">
-        <v>78.019138</v>
+        <v>113.018772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>k_現貨 1.50</t>
+          <t>k_長約 1.00</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.278726</v>
+        <v>39.19802</v>
       </c>
       <c r="C5" t="n">
-        <v>56.355898</v>
+        <v>32.911313</v>
       </c>
       <c r="D5" t="n">
-        <v>65.87808800000001</v>
+        <v>33.375786</v>
       </c>
       <c r="E5" t="n">
-        <v>40.736305</v>
+        <v>55.795512</v>
       </c>
       <c r="F5" t="n">
-        <v>37.512969</v>
+        <v>46.891325</v>
       </c>
       <c r="G5" t="n">
-        <v>46.176773</v>
+        <v>57.191432</v>
       </c>
       <c r="H5" t="n">
-        <v>52.419591</v>
+        <v>64.120262</v>
       </c>
       <c r="I5" t="n">
-        <v>63.15741</v>
+        <v>75.06137099999999</v>
       </c>
       <c r="J5" t="n">
-        <v>90.50626</v>
+        <v>107.652395</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>k_現貨 2.30</t>
+          <t>k_長約 0.91（Nebius–Microsoft：Vineland 300 MW 視為 IT）</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>164.837284</v>
+        <v>33.922017</v>
       </c>
       <c r="C6" t="n">
-        <v>150.066959</v>
+        <v>27.085639</v>
       </c>
       <c r="D6" t="n">
-        <v>190.062517</v>
+        <v>25.891792</v>
       </c>
       <c r="E6" t="n">
-        <v>10.73406</v>
+        <v>58.855892</v>
       </c>
       <c r="F6" t="n">
-        <v>9.356047</v>
+        <v>49.564719</v>
       </c>
       <c r="G6" t="n">
-        <v>8.644563</v>
+        <v>59.761779</v>
       </c>
       <c r="H6" t="n">
-        <v>29.967352</v>
+        <v>67.52091900000001</v>
       </c>
       <c r="I6" t="n">
-        <v>40.379361</v>
+        <v>78.49880899999999</v>
       </c>
       <c r="J6" t="n">
-        <v>59.312161</v>
+        <v>112.043335</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>長約占比 下緣（合約 MW 下緣）</t>
+          <t>k_長約 1.09（Nebius–Microsoft：Vineland 300 MW 視為設施（÷ PUE 1.2））</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.02297900000001</v>
+        <v>44.763467</v>
       </c>
       <c r="C7" t="n">
-        <v>82.722585</v>
+        <v>39.039385</v>
       </c>
       <c r="D7" t="n">
-        <v>98.099101</v>
+        <v>40.978626</v>
       </c>
       <c r="E7" t="n">
-        <v>26.257043</v>
+        <v>52.62101</v>
       </c>
       <c r="F7" t="n">
-        <v>22.992282</v>
+        <v>44.219776</v>
       </c>
       <c r="G7" t="n">
-        <v>27.979139</v>
+        <v>54.327318</v>
       </c>
       <c r="H7" t="n">
-        <v>40.603349</v>
+        <v>60.72139</v>
       </c>
       <c r="I7" t="n">
-        <v>51.234626</v>
+        <v>71.62571800000001</v>
       </c>
       <c r="J7" t="n">
-        <v>75.814024</v>
+        <v>103.263239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>長約占比 上緣（合約 MW 上緣，含 Meta 承購）</t>
+          <t>k_長約 1.33（Nebius–Microsoft：約 10 萬顆 GB300（Bloomberg））</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.453246</v>
+        <v>61.083424</v>
       </c>
       <c r="C8" t="n">
-        <v>56.505856</v>
+        <v>56.568912</v>
       </c>
       <c r="D8" t="n">
-        <v>71.13004100000001</v>
+        <v>62.476492</v>
       </c>
       <c r="E8" t="n">
-        <v>39.920551</v>
+        <v>41.259681</v>
       </c>
       <c r="F8" t="n">
-        <v>38.977347</v>
+        <v>36.213962</v>
       </c>
       <c r="G8" t="n">
-        <v>43.716765</v>
+        <v>45.57993</v>
       </c>
       <c r="H8" t="n">
-        <v>53.320568</v>
+        <v>51.655654</v>
       </c>
       <c r="I8" t="n">
-        <v>63.953718</v>
+        <v>62.461898</v>
       </c>
       <c r="J8" t="n">
-        <v>88.631249</v>
+        <v>91.556748</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tokenomics 低成本（錨與建置成本同動；k 依證據重算）</t>
+          <t>隨需占比 10%（k_現貨 1.76）</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139.038338</v>
+        <v>31.147222</v>
       </c>
       <c r="C9" t="n">
-        <v>123.038047</v>
+        <v>23.781062</v>
       </c>
       <c r="D9" t="n">
-        <v>156.554298</v>
+        <v>21.854846</v>
       </c>
       <c r="E9" t="n">
-        <v>8.266173999999999</v>
+        <v>60.648291</v>
       </c>
       <c r="F9" t="n">
-        <v>6.334469</v>
+        <v>50.82757</v>
       </c>
       <c r="G9" t="n">
-        <v>3.758318</v>
+        <v>61.163634</v>
       </c>
       <c r="H9" t="n">
-        <v>23.956945</v>
+        <v>69.409274</v>
       </c>
       <c r="I9" t="n">
-        <v>32.982453</v>
+        <v>80.40759799999999</v>
       </c>
       <c r="J9" t="n">
-        <v>49.850095</v>
+        <v>114.481847</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tokenomics 高成本（錨與建置成本同動；k 依證據重算）</t>
+          <t>隨需占比 20%（k_現貨 1.76）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.825596</v>
+        <v>36.818671</v>
       </c>
       <c r="C10" t="n">
-        <v>57.930031</v>
+        <v>30.286058</v>
       </c>
       <c r="D10" t="n">
-        <v>63.752928</v>
+        <v>30.008928</v>
       </c>
       <c r="E10" t="n">
-        <v>53.154264</v>
+        <v>57.155688</v>
       </c>
       <c r="F10" t="n">
-        <v>50.762776</v>
+        <v>48.079507</v>
       </c>
       <c r="G10" t="n">
-        <v>58.849996</v>
+        <v>58.333815</v>
       </c>
       <c r="H10" t="n">
-        <v>69.706028</v>
+        <v>65.631671</v>
       </c>
       <c r="I10" t="n">
-        <v>82.312651</v>
+        <v>76.589128</v>
       </c>
       <c r="J10" t="n">
-        <v>115.489081</v>
+        <v>109.60393</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>首期末爬坡 50%</t>
+          <t>Tokenomics 低成本（錨與建置成本同動；k 依證據重算）</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81.335751</v>
+        <v>32.864346</v>
       </c>
       <c r="C11" t="n">
-        <v>72.230073</v>
+        <v>24.128738</v>
       </c>
       <c r="D11" t="n">
-        <v>87.50499000000001</v>
+        <v>24.487414</v>
       </c>
       <c r="E11" t="n">
-        <v>31.096824</v>
+        <v>47.380887</v>
       </c>
       <c r="F11" t="n">
-        <v>28.642002</v>
+        <v>37.609166</v>
       </c>
       <c r="G11" t="n">
-        <v>33.666394</v>
+        <v>45.453437</v>
       </c>
       <c r="H11" t="n">
-        <v>45.430771</v>
+        <v>53.383301</v>
       </c>
       <c r="I11" t="n">
-        <v>56.062701</v>
+        <v>62.854192</v>
       </c>
       <c r="J11" t="n">
-        <v>80.687453</v>
+        <v>90.98583499999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Tokenomics 高成本（錨與建置成本同動；k 依證據重算）</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>61.727885</v>
+      </c>
+      <c r="F12" t="n">
+        <v>61.727885</v>
+      </c>
+      <c r="G12" t="n">
+        <v>61.727885</v>
+      </c>
+      <c r="H12" t="n">
+        <v>99.421916</v>
+      </c>
+      <c r="I12" t="n">
+        <v>112.438147</v>
+      </c>
+      <c r="J12" t="n">
+        <v>156.498663</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>首期末爬坡 50%</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>23.46055</v>
+      </c>
+      <c r="C13" t="n">
+        <v>17.218652</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11.925944</v>
+      </c>
+      <c r="E13" t="n">
+        <v>61.430877</v>
+      </c>
+      <c r="F13" t="n">
+        <v>53.382879</v>
+      </c>
+      <c r="G13" t="n">
+        <v>61.727885</v>
+      </c>
+      <c r="H13" t="n">
+        <v>73.376538</v>
+      </c>
+      <c r="I13" t="n">
+        <v>84.41573099999999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>119.550168</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>首期末爬坡 80%</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>82.576662</v>
-      </c>
-      <c r="C12" t="n">
-        <v>73.13361399999999</v>
-      </c>
-      <c r="D12" t="n">
-        <v>88.42730899999999</v>
-      </c>
-      <c r="E12" t="n">
-        <v>30.764479</v>
-      </c>
-      <c r="F12" t="n">
-        <v>28.309657</v>
-      </c>
-      <c r="G12" t="n">
-        <v>33.332677</v>
-      </c>
-      <c r="H12" t="n">
-        <v>44.513988</v>
-      </c>
-      <c r="I12" t="n">
-        <v>55.145919</v>
-      </c>
-      <c r="J12" t="n">
-        <v>79.737708</v>
+      <c r="B14" t="n">
+        <v>23.572689</v>
+      </c>
+      <c r="C14" t="n">
+        <v>17.306903</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12.484615</v>
+      </c>
+      <c r="E14" t="n">
+        <v>60.860116</v>
+      </c>
+      <c r="F14" t="n">
+        <v>52.812119</v>
+      </c>
+      <c r="G14" t="n">
+        <v>61.575003</v>
+      </c>
+      <c r="H14" t="n">
+        <v>72.811987</v>
+      </c>
+      <c r="I14" t="n">
+        <v>83.85118</v>
+      </c>
+      <c r="J14" t="n">
+        <v>118.983419</v>
       </c>
     </row>
   </sheetData>
@@ -3677,7 +3746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3732,7 +3801,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>(d)② 套用 k</t>
+          <t>(d)② 套用 k（第 1 輪口徑）</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -3747,30 +3816,45 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>v0.3</t>
+          <t>＝第 1 輪</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>(d)⑤ 新增產能按長約價（W4 r2）</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>(d)⑥ 公司合約 k（未採用）</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>v0.3（第 2 輪）</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>總變動</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>融資前缺口 v0.2</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>融資前缺口 v0.3</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>股權募資 v0.2</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>股權募資 v0.3</t>
         </is>
@@ -3810,19 +3894,28 @@
         <v>81.75343212213843</v>
       </c>
       <c r="K3" t="n">
-        <v>46.60060623816278</v>
+        <v>-58.25517938123691</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>23.49825274090152</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-11.65457314307413</v>
+      </c>
+      <c r="O3" t="n">
         <v>66.59326650391792</v>
       </c>
-      <c r="M3" t="n">
-        <v>45.12156030790113</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
+        <v>73.1861273413288</v>
+      </c>
+      <c r="Q3" t="n">
         <v>57.94194652934092</v>
       </c>
-      <c r="O3" t="n">
-        <v>30.98473137702997</v>
+      <c r="R3" t="n">
+        <v>61.23837137048206</v>
       </c>
     </row>
     <row r="4">
@@ -3859,19 +3952,28 @@
         <v>72.53416790168438</v>
       </c>
       <c r="K4" t="n">
-        <v>10.81422270595173</v>
+        <v>-55.28585138423146</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17.24831651745292</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-44.47162867827973</v>
+      </c>
+      <c r="O4" t="n">
         <v>59.82576600598858</v>
       </c>
-      <c r="M4" t="n">
-        <v>55.75349074607533</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
+        <v>84.22532040043986</v>
+      </c>
+      <c r="Q4" t="n">
         <v>33.73549244320962</v>
       </c>
-      <c r="O4" t="n">
-        <v>28.52990918473726</v>
+      <c r="R4" t="n">
+        <v>53.1903743091246</v>
       </c>
     </row>
     <row r="5">
@@ -3908,19 +4010,28 @@
         <v>87.81545068541499</v>
       </c>
       <c r="K5" t="n">
-        <v>-66.6808926486238</v>
+        <v>-75.66486344896123</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12.15058723645376</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-142.345756097585</v>
+      </c>
+      <c r="O5" t="n">
         <v>62.03000505436319</v>
       </c>
-      <c r="M5" t="n">
-        <v>80.36712457344927</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
+        <v>119.35901618683</v>
+      </c>
+      <c r="Q5" t="n">
         <v>10.98900547553735</v>
       </c>
-      <c r="O5" t="n">
-        <v>33.55383821545667</v>
+      <c r="R5" t="n">
+        <v>61.72788480000001</v>
       </c>
     </row>
   </sheetData>
@@ -3952,7 +4063,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>只評估並列、不切換（工作單預設 7）；是否切換由 Andy 決定。穩態 EBITDA 率 59%／70%／75% 時基準目標價 $132.2／$203.7／$236.0</t>
+          <t>只評估並列、不切換（工作單預設 7；第 2 輪保留）；是否切換由 Andy 決定。穩態 EBITDA 率 59%／70%／75% 時基準目標價 $26.5／$35.4／$39.6</t>
         </is>
       </c>
     </row>
@@ -4127,19 +4238,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.15913942625215</v>
+        <v>8.825199907724254</v>
       </c>
       <c r="C9" t="n">
-        <v>15.04667220393632</v>
+        <v>9.21179827155456</v>
       </c>
       <c r="D9" t="n">
-        <v>17.970334094296</v>
+        <v>9.406764831885297</v>
       </c>
       <c r="E9" t="n">
-        <v>19.20577108987948</v>
+        <v>9.488753147301413</v>
       </c>
       <c r="F9" t="n">
-        <v>19.87481714355207</v>
+        <v>9.532645136058623</v>
       </c>
     </row>
     <row r="10">
@@ -4149,19 +4260,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8249936026068225</v>
+        <v>0.7192199602178673</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8308447172624079</v>
+        <v>0.7236995409706046</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8564769956373182</v>
+        <v>0.725818984028159</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8649663330152638</v>
+        <v>0.7266842484701559</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8691276150768177</v>
+        <v>0.7271413461464225</v>
       </c>
     </row>
     <row r="11">
@@ -4184,6 +4295,447 @@
       </c>
       <c r="F11" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>已決定事項 15：差距 &gt; 10% 需有證據的機制才調整；找不到機制則維持 Tokenomics／現行值，公司實際列敏感度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>參數</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Tokenomics 值</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Tokenomics</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Nebius 實際</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>實際</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>差距</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>機制與證據</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>公司調整</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>採用值</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>標記</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>來源網址</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>每 MW 年收入（定價倍數 k）</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IF_HoldEcon × k_長約 0.76：FY26 8.83 US$m/MW（錨 11.61）</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Q2 AI cloud 營收 574.9 × 4 ÷ 季末在役 366 MW（內插）＝6.28 US$m/MW（Q2 2026 6-K 附註 15 分部營收 [Interested-party]；在役 MW 為 [Derived] 內插）</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.2888</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>找到：爬坡——Q2 股東信「brought additional capacity online across sites in the US and Europe during the second half of the second quarter」「delivered all capacity tranches to Microsoft」：新容量在季末前才上線，季內計費 MW 低於季末在役 MW。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>沿用既有機制：期初可計費 MW＝Q2 營收 × 4 ÷ 首期每 MW 年收入（264 ÷ 366＝72%），爬坡係數 60%／80%／100%，FY28 起回到全額計費；k 不調整</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>k＝0.76（市場長約）；每 MW 年收入 8.83 → 9.53</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>[Derived]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1513845/000110465926094844/nbis-20260812xex99d2.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>定價倍數 k：Nebius 自身合約（Microsoft）</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>k_長約 0.76（IREN–Microsoft）</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>17.4bn ÷ 5 年 ÷ 假設容量 ÷ 12.72：0.91（300 MW 視為 IT）／1.09（視為設施）／1.33（約 10 萬顆 GB300）（Microsoft 協議 6-K 2025-09-08、Q3 2025 附註（TCV、5 年、Vineland 分批）[Interested-party]；容量為 Nebius 站點新聞稿與 Bloomberg 引述 [Assumed]）</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>找不到可用的已揭露條款：合約未揭露 MW 或 GPU 數，換算必須假設容量（已決定事項 15 要求完全由已揭露條款算出）。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>不調整；列敏感度（k_長約 0.91／1.09／1.33）</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>k_長約 0.76</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>[Derived]／[Assumed]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1513845/000110465925088312/tm2525580d1_6k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>營運現金成本（不含 D&amp;A，每 MW）</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IF_OpexGW（季末世代加權）2.44 US$m/MW·年（電費 0.67、IT 維護、廠房維護、人員軟體、稅險）</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q2 營業成本（不含 D&amp;A）133.6 × 4 ÷ 366 MW＝1.46（Q2 2026 6-K 損益表 [Interested-party]）</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.4016</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>未找到有證據的機制：可能來源——(a) 爬坡分母（季均在役 MW 低於季末 366，方向成立但幅度無法量化）；(b) IT 維護在保固期內（未找到 Nebius 保固條款）；(c) 營業成本口徑不含人員、稅險（未證實）。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>不調整（模型營運成本採 EBITDA 率路徑，不使用 Tokenomics 由下而上；第 1 輪結論保留）；Nebius 實際列為對照</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>EBITDA 率路徑（不切換）</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>[Derived]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1513845/000110465926094844/nbis-20260812xex99d2.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EBITDA 率</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>由下而上隱含（未扣管銷與租金）：1 − 2.48 ÷ 8.83＝71.9%（FY26）</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Q2 AI cloud 分部調整後 EBITDA 285.7 ÷ 574.9＝49.7%（合併 236.2 ÷ 582.3＝40.6%）（Q2 2026 6-K 附註 15 [Interested-party]）</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.3088</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>找到：管銷、研發與分部費用（Q2 合併營收 582.3 − 營業成本 133.6 − 調整後 EBITDA 236.2＝212.5，約占 36%）不在 Tokenomics 範圍。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>已在模型：EBITDA 率起點＝Q2 AI cloud 分部實際 49.7%，線性走向 47%（可觀察 neocloud 區間中點）；何時回到 Tokenomics：不回（成本端是否切換待 Andy 決定）</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>49.7% → 47%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>[Interested-party]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1513845/000110465926094844/nbis-20260812xex99d2.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>每 MW 資本支出</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IF_CapexTotal GB300 50.12／VR200 50.26 US$m/MW-IT</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>H1 現金資本支出 8,130 ÷ H1 新增在役 196 MW（366 − 170，內插）＝41.5（含預建，在建工程 7,836）；在役資產（毛額 − 在建）6,313 ÷ 366＝17.2（Q1／Q2 2026 6-K 現金流量表與 PP&amp;E 附註 [Interested-party]；MW 為 [Derived] 內插）</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.172</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>未找到有證據的機制：H1 數字混入預建（在建工程）、在役 MW 為內插、部分站點為租賃（營業租賃負債 1,625），無法分離每 MW 單價；模型 FY26 全年 CapEx 29.1 對公司指引 20–25（中點 +29%）方向一致但口徑（應計 vs 現金、預建）不明。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>不調整（維持 Tokenomics 50.12）；公司實際列敏感度：每 MW 建置成本 × 0.83（41.5 ÷ 50.1）基準目標價 $20.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50.12／50.26</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>[Derived]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1513845/000110465926094844/nbis-20260812xex99d2.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GPU 折舊年限</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IF_DeprLifeIT 6 年</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>伺服器與網通設備 5 年（2026-01-01 起由 4 年延長）（Q1／Q2 2026 6-K 附註（會計估計變更）[Interested-party]）</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.1667</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>找到：公司會計政策（6-K 附註）。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>已在模型：GPU 經濟壽命 5 年（defaults.gpuLife）；會計政策，不回到 Tokenomics 值</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5 年</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>[Interested-party]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1513845/000110465926094844/nbis-20260812xex99d2.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>電費</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IF_PowerCost 0.67 US$m/MW·年（0.08 $/kWh、平均用電 80%、PUE 1.2）</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>電力與能源最低承諾 2027 年 541.8（對應 MW 未揭露）（Q2 2026 6-K 附註 11 [Interested-party]）</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>無法對照：承諾金額對應的 MW 與電價未揭露（找不到）。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>不調整（模型以 EBITDA 率路徑涵蓋）</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1513845/000110465926094844/nbis-20260812xex99d2.htm</t>
+        </is>
       </c>
     </row>
   </sheetData>
